--- a/modele-import-ISG.xlsx
+++ b/modele-import-ISG.xlsx
@@ -541,7 +541,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>• Destinations : seules la Ville et le Pays sont obligatoires. Si Latitude et Longitude sont vides, l'app les cherche toute seule (connexion Internet nécessaire).</t>
+          <t>• Destinations : seules la Ville et le Pays sont obligatoires. La photo de la ville (lien) est facultative : sinon, utilisez Données › Destinations › Photos automatiques. Si Latitude et Longitude sont vides, l'app les cherche toute seule (connexion Internet nécessaire).</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,8 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -647,10 +648,16 @@
           <t>Présentation</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Photo de la ville (lien)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Obligatoires : Ville, Pays.
-Latitude / Longitude : facultatives (recherche automatique).</t>
+Latitude / Longitude : facultatives (recherche automatique).
+Photo de la ville : facultative. Laissez vide pour la chercher ensuite dans Données › Photos automatiques.</t>
         </is>
       </c>
     </row>
@@ -686,6 +693,7 @@
           <t>Capitale vivante, au cœur de l'Espagne : cours en espagnol et en anglais, vie étudiante animée.</t>
         </is>
       </c>
+      <c r="H2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -715,6 +723,7 @@
           <t>Ville méditerranéenne ouverte sur le monde. (Latitude et longitude vides : trouvées automatiquement.)</t>
         </is>
       </c>
+      <c r="H3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -724,6 +733,7 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -733,6 +743,7 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -742,6 +753,7 @@
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -751,6 +763,7 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -760,6 +773,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -769,6 +783,7 @@
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -778,6 +793,7 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -787,6 +803,7 @@
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -796,6 +813,7 @@
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -805,6 +823,7 @@
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -814,6 +833,7 @@
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -823,6 +843,7 @@
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -832,6 +853,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -841,6 +863,7 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -850,6 +873,7 @@
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -859,6 +883,7 @@
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -868,6 +893,7 @@
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -877,6 +903,7 @@
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -886,6 +913,7 @@
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -895,6 +923,7 @@
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -904,6 +933,7 @@
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -913,6 +943,7 @@
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -922,6 +953,7 @@
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -931,6 +963,7 @@
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -940,6 +973,7 @@
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -949,6 +983,7 @@
       <c r="E29" s="6" t="n"/>
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -958,6 +993,7 @@
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -967,6 +1003,7 @@
       <c r="E31" s="6" t="n"/>
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -976,6 +1013,7 @@
       <c r="E32" s="6" t="n"/>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -985,6 +1023,7 @@
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -994,6 +1033,7 @@
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1003,6 +1043,7 @@
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1012,6 +1053,7 @@
       <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1021,6 +1063,7 @@
       <c r="E37" s="6" t="n"/>
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1030,6 +1073,7 @@
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1039,6 +1083,7 @@
       <c r="E39" s="6" t="n"/>
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1048,6 +1093,7 @@
       <c r="E40" s="6" t="n"/>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1057,6 +1103,7 @@
       <c r="E41" s="6" t="n"/>
       <c r="F41" s="6" t="n"/>
       <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1066,6 +1113,7 @@
       <c r="E42" s="6" t="n"/>
       <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1075,6 +1123,7 @@
       <c r="E43" s="6" t="n"/>
       <c r="F43" s="6" t="n"/>
       <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1084,6 +1133,7 @@
       <c r="E44" s="6" t="n"/>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1093,6 +1143,7 @@
       <c r="E45" s="6" t="n"/>
       <c r="F45" s="6" t="n"/>
       <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -1102,6 +1153,7 @@
       <c r="E46" s="6" t="n"/>
       <c r="F46" s="6" t="n"/>
       <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -1111,6 +1163,7 @@
       <c r="E47" s="6" t="n"/>
       <c r="F47" s="6" t="n"/>
       <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -1120,6 +1173,7 @@
       <c r="E48" s="6" t="n"/>
       <c r="F48" s="6" t="n"/>
       <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -1129,6 +1183,7 @@
       <c r="E49" s="6" t="n"/>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -1138,6 +1193,7 @@
       <c r="E50" s="6" t="n"/>
       <c r="F50" s="6" t="n"/>
       <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -1147,6 +1203,7 @@
       <c r="E51" s="6" t="n"/>
       <c r="F51" s="6" t="n"/>
       <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -1156,6 +1213,7 @@
       <c r="E52" s="6" t="n"/>
       <c r="F52" s="6" t="n"/>
       <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -1165,6 +1223,7 @@
       <c r="E53" s="6" t="n"/>
       <c r="F53" s="6" t="n"/>
       <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -1174,6 +1233,7 @@
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="6" t="n"/>
       <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -1183,6 +1243,7 @@
       <c r="E55" s="6" t="n"/>
       <c r="F55" s="6" t="n"/>
       <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -1192,6 +1253,7 @@
       <c r="E56" s="6" t="n"/>
       <c r="F56" s="6" t="n"/>
       <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -1201,6 +1263,7 @@
       <c r="E57" s="6" t="n"/>
       <c r="F57" s="6" t="n"/>
       <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -1210,6 +1273,7 @@
       <c r="E58" s="6" t="n"/>
       <c r="F58" s="6" t="n"/>
       <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -1219,6 +1283,7 @@
       <c r="E59" s="6" t="n"/>
       <c r="F59" s="6" t="n"/>
       <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -1228,6 +1293,7 @@
       <c r="E60" s="6" t="n"/>
       <c r="F60" s="6" t="n"/>
       <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1240,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1255,7 +1321,11 @@
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1319,9 +1389,30 @@
           <t>Durée (s)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Séjour</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Parcours (texte)</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Conseil</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Mots-clés</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Colonnes utiles : Ville, Lien vidéo.
+Séjour, Parcours, Conseil, Mots-clés : alimentent la fiche étudiant (« En savoir plus »).
 Format : Automatique / Paysage / Portrait.
 Lien vignette : image facultative (sinon une image est proposée depuis la vidéo).</t>
         </is>
@@ -1374,6 +1465,26 @@
       <c r="L2" s="5" t="n">
         <v>30</v>
       </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Semestre 5 · 5 mois</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi Madrid, ce que j'y ai fait, ce que ça a changé.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Anticipez vos démarches.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>Culture, Langues</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1421,6 +1532,18 @@
       </c>
       <c r="L3" s="5" t="n">
         <v>45</v>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Année complète</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>Stage, Autonomie</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1436,6 +1559,10 @@
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -1450,6 +1577,10 @@
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -1464,6 +1595,10 @@
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -1478,6 +1613,10 @@
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -1492,6 +1631,10 @@
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -1506,6 +1649,10 @@
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -1520,6 +1667,10 @@
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -1534,6 +1685,10 @@
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
       <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -1548,6 +1703,10 @@
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1562,6 +1721,10 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -1576,6 +1739,10 @@
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
       <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -1590,6 +1757,10 @@
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -1604,6 +1775,10 @@
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1618,6 +1793,10 @@
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1632,6 +1811,10 @@
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1646,6 +1829,10 @@
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1660,6 +1847,10 @@
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1674,6 +1865,10 @@
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1688,6 +1883,10 @@
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1702,6 +1901,10 @@
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1716,6 +1919,10 @@
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1730,6 +1937,10 @@
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1744,6 +1955,10 @@
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1758,6 +1973,10 @@
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1772,6 +1991,10 @@
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1786,6 +2009,10 @@
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
       <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1800,6 +2027,10 @@
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1814,6 +2045,10 @@
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1828,6 +2063,10 @@
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1842,6 +2081,10 @@
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1856,6 +2099,10 @@
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1870,6 +2117,10 @@
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
       <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
+      <c r="N35" s="6" t="n"/>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1884,6 +2135,10 @@
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1898,6 +2153,10 @@
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1912,6 +2171,10 @@
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
+      <c r="N38" s="6" t="n"/>
+      <c r="O38" s="6" t="n"/>
+      <c r="P38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1926,6 +2189,10 @@
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
       <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
+      <c r="N39" s="6" t="n"/>
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1940,6 +2207,10 @@
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
       <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="6" t="n"/>
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1954,6 +2225,10 @@
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
       <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1968,6 +2243,10 @@
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="6" t="n"/>
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1982,6 +2261,10 @@
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
       <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1996,6 +2279,10 @@
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -2010,6 +2297,10 @@
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="6" t="n"/>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -2024,6 +2315,10 @@
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="6" t="n"/>
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -2038,6 +2333,10 @@
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="6" t="n"/>
+      <c r="O47" s="6" t="n"/>
+      <c r="P47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -2052,6 +2351,10 @@
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
+      <c r="N48" s="6" t="n"/>
+      <c r="O48" s="6" t="n"/>
+      <c r="P48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -2066,6 +2369,10 @@
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
       <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="6" t="n"/>
+      <c r="O49" s="6" t="n"/>
+      <c r="P49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -2080,6 +2387,10 @@
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
+      <c r="N50" s="6" t="n"/>
+      <c r="O50" s="6" t="n"/>
+      <c r="P50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -2094,6 +2405,10 @@
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
       <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="6" t="n"/>
+      <c r="O51" s="6" t="n"/>
+      <c r="P51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -2108,6 +2423,10 @@
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
+      <c r="N52" s="6" t="n"/>
+      <c r="O52" s="6" t="n"/>
+      <c r="P52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -2122,6 +2441,10 @@
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
       <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="6" t="n"/>
+      <c r="O53" s="6" t="n"/>
+      <c r="P53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -2136,6 +2459,10 @@
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="6" t="n"/>
+      <c r="M54" s="6" t="n"/>
+      <c r="N54" s="6" t="n"/>
+      <c r="O54" s="6" t="n"/>
+      <c r="P54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -2150,6 +2477,10 @@
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="6" t="n"/>
+      <c r="M55" s="6" t="n"/>
+      <c r="N55" s="6" t="n"/>
+      <c r="O55" s="6" t="n"/>
+      <c r="P55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -2164,6 +2495,10 @@
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="6" t="n"/>
       <c r="L56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
+      <c r="N56" s="6" t="n"/>
+      <c r="O56" s="6" t="n"/>
+      <c r="P56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -2178,6 +2513,10 @@
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
       <c r="L57" s="6" t="n"/>
+      <c r="M57" s="6" t="n"/>
+      <c r="N57" s="6" t="n"/>
+      <c r="O57" s="6" t="n"/>
+      <c r="P57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -2192,6 +2531,10 @@
       <c r="J58" s="6" t="n"/>
       <c r="K58" s="6" t="n"/>
       <c r="L58" s="6" t="n"/>
+      <c r="M58" s="6" t="n"/>
+      <c r="N58" s="6" t="n"/>
+      <c r="O58" s="6" t="n"/>
+      <c r="P58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -2206,6 +2549,10 @@
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
       <c r="L59" s="6" t="n"/>
+      <c r="M59" s="6" t="n"/>
+      <c r="N59" s="6" t="n"/>
+      <c r="O59" s="6" t="n"/>
+      <c r="P59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -2220,6 +2567,10 @@
       <c r="J60" s="6" t="n"/>
       <c r="K60" s="6" t="n"/>
       <c r="L60" s="6" t="n"/>
+      <c r="M60" s="6" t="n"/>
+      <c r="N60" s="6" t="n"/>
+      <c r="O60" s="6" t="n"/>
+      <c r="P60" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/modele-import-ISG.xlsx
+++ b/modele-import-ISG.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Destinations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Témoignages" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profils" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -496,7 +496,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Remplissez les feuilles « Destinations », « Témoignages » et « Photos » (les lignes grises sont des exemples : supprimez-les ou remplacez-les).</t>
+          <t>1. Remplissez les feuilles « Destinations », « Profils » et « Photos » (les lignes grises sont des exemples : supprimez-les ou remplacez-les).</t>
         </is>
       </c>
     </row>
@@ -548,14 +548,15 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>• Témoignages et Photos : la colonne Ville (et Pays si deux villes portent le même nom) indique la destination concernée.</t>
+          <t>• Profils et Photos : la colonne Ville (et Pays si deux villes portent le même nom) indique la destination concernée.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• Liens vidéo acceptés : fichier direct (.mp4), YouTube, Vimeo, Google Drive, Dropbox. Un lien YouTube/Vimeo/Drive ne fonctionne qu'avec Internet.</t>
+          <t>• Profils : un voyage peut avoir plusieurs profils (une ligne par étudiant·e). Le lien vidéo est facultatif : sans vidéo, la fiche du profil s'affiche quand même.
+• Liens vidéo acceptés : fichier direct (.mp4), YouTube, Vimeo, Google Drive, Dropbox. Un lien YouTube/Vimeo/Drive ne fonctionne qu'avec Internet.</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1412,7 @@
       </c>
       <c r="R1" s="2" t="inlineStr">
         <is>
-          <t>Colonnes utiles : Ville, Lien vidéo.
+          <t>Colonnes utiles : Ville et Prénom (la vidéo est facultative).
 Séjour, Parcours, Conseil, Mots-clés : alimentent la fiche étudiant (« En savoir plus »).
 Format : Automatique / Paysage / Portrait.
 Lien vignette : image facultative (sinon une image est proposée depuis la vidéo).</t>
